--- a/Phase6.2/quantized (Cleaned)/load_14.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_14.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9404 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$499</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="499"/>
+                <c:pt idx="0">
+                  <c:v>24.9936</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.6025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.0878</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.6389</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.1484</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.6819</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.1374</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12.3023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.3182</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13.1709</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.0397</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.077</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.0212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.624</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.7678</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.7682</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.2494</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.1228</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>27.7359</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>51.6137</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.1756</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18.1412</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>29.0573</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23.1447</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18.8332</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26.8574</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>47.9841</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>47.5128</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>19.9524</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>20.5547</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.39</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>23.6185</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>16.2209</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.8181</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>28.6872</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>11.6695</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>13.9502</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12.4802</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>13.6856</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>12.1678</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>17.2257</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.873</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>11.4332</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.5413</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>16.5071</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>22.1386</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15.406</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>13.3012</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>20.5077</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>11.8608</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>11.4548</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>17.9335</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>13.5167</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>11.9757</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9.7553</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>12.6331</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>11.9156</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>11.9786</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15.7078</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>29.5468</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>11.5184</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15.7885</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.3605</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>11.2408</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>16.6373</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>17.3924</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>21.1992</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.1244</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10.876</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.7054</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>14.4472</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.1025</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>13.9304</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>14.8878</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>13.6981</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>15.7699</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9.9385</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>12.8494</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>17.6122</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>13.1514</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>12.3627</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>14.7577</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>14.1117</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>11.7451</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10.4775</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>11.3258</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>13.6824</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>27.4362</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>26.5852</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>15.2025</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>15.406</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>15.5181</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>17.9067</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>18.3272</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>13.9558</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>25.0758</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>12.8567</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>16.6563</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>19.9844</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>11.4566</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10.4816</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>17.0559</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>18.7052</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>14.5366</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>13.2391</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>11.0445</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>13.5217</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>12.9759</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>20.9623</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>11.3709</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>20.133</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>25.4019</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>14.1675</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>18.8814</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>13.407</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>25.6444</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>11.0513</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>11.8537</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>13.9686</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>10.9891</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>11.8659</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>22.4071</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>14.9195</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>16.3706</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>15.6491</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>11.5697</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>11.0141</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>11.7698</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>17.7083</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>13.9888</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>12.301</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>20.3818</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>16.0973</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>13.0774</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>14.6946</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>11.5294</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>17.3012</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>20.8004</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>19.1328</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>21.6871</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>16.2255</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>12.0691</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>20.0595</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>17.5316</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>12.8945</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>12.2856</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>11.567</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>12.151</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>13.5097</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>12.0614</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>10.4593</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>10.9608</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>16.8263</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>17.3062</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>13.0563</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>19.022</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>11.5133</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>19.3967</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>11.0358</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>12.4482</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>9.8928</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>14.434</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>11.093</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>19.6789</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>14.0735</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>18.3395</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>12.6237</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>22.7482</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>10.9413</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>14.9488</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>13.4925</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>19.5153</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>10.1849</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>11.4657</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>12.9258</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>10.423</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>11.6528</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>11.2105</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>11.1375</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>14.1638</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>11.6551</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>10.8619</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>11.0082</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>15.4396</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>15.8872</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>19.1328</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>22.7469</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>12.7293</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>13.9981</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>11.3647</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>12.1087</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>15.9799</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>16.7708</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>11.2119</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>11.3105</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>11.9638</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>13.9807</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>14.4702</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>14.679</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>11.2363</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>14.8335</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>14.7141</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>18.0427</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>13.1224</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>21.4825</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>18.6699</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>18.6434</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>11.4104</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>14.1886</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>23.9884</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>10.3397</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>13.5864</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>12.5756</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>12.9022</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>15.0687</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>14.8211</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>12.6254</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>12.3382</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>18.1715</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>16.9033</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>11.44</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>20.137</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>17.1696</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>18.3254</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>11.0816</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>12.598</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>10.9496</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>15.3993</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>21.0229</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>20.159</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>11.7714</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>18.2505</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>11.1383</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>14.7758</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>18.7319</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>20.4468</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>12.2616</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>21.7749</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>12.2191</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>15.9892</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>10.3556</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>11.6843</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>16.3504</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>23.0511</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>9.7835</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>15.2668</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>20.2245</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>18.1726</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>11.9669</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>14.6596</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>13.1762</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>16.0235</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>14.986</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>20.146</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>17.8519</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>14.8108</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>22.1304</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>15.8485</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>15.9575</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>19.2487</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>21.0914</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>18.9216</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>14.4373</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>17.5744</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>12.1129</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>13.1307</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>19.198</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>11.222</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>12.0779</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>12.313</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>11.1882</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>12.1246</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>20.2274</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>15.1014</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>16.5259</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>17.2309</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>13.7777</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>12.1037</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>16.64</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>15.389</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>13.5951</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>12.0428</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>11.3284</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>20.0767</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>13.4819</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>27.8975</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>11.7402</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>19.1765</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>11.528</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>18.8248</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>11.8121</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>11.6652</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>11.1711</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>16.6225</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>15.402</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>12.5209</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>12.336</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>13.5704</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>17.808</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>11.828</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>10.8771</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>23.4105</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>10.6278</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>17.217</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.4356</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>17.6853</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>72.0189</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>23.2699</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>10.6781</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>11.4696</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>13.0345</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>13.9233</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>11.0264</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>11.8347</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>11.3117</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>23.1588</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>18.3547</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>11.8904</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>10.9487</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>11.2707</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>18.3518</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>12.1302</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>17.5756</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>15.3854</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>13.9717</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>16.282</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>12.8795</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>13.7909</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>23.864</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>16.8576</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>16.6041</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>12.547</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>19.7643</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>12.833</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>21.145</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>11.6857</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>12.0014</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>12.5229</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>11.6819</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>23.5704</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>16.6402</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>20.2087</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>15.2274</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>11.7194</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>14.0721</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>15.2602</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>14.7607</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>16.72</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>17.4623</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>17.9243</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>10.3045</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>21.1974</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>11.1425</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>19.8947</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>14.4061</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>22.1141</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>11.516</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>23.5829</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>15.2763</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>19.9742</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>11.8555</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>19.582</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>19.2064</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>13.2815</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>12.6353</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>11.6563</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>19.1206</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>12.7935</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>19.7637</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>13.025</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>26.8212</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>16.3172</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>15.9872</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>11.91</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>11.6652</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>11.5788</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>11.2658</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>17.1082</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>13.1698</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>21.8559</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>21.9557</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>10.665</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>18.3047</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>18.057</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>22.3629</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>14.8818</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>20.1783</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>10.7452</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>20.2297</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>21.537</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>11.0176</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>11.2579</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>17.0567</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>11.746</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>15.7689</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>14.1562</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>13.0158</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>12.1658</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>16.5938</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>15.2999</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>19.2096</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>15.6607</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>13.1456</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>11.7875</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>18.0658</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>21.6358</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>11.0346</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>18.1341</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>17.5536</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>11.8916</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>19.2974</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>19.8457</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>10.282</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>15.4067</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>13.6152</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>19.0586</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>16.4692</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>13.5607</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>13.0473</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>11.2694</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>17.3316</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>12.6457</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>11.9886</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>10.8179</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>18.1218</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>20.2342</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>16.2704</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>11.7725</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>16.3269</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>23.1139</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>10.2137</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>12.1437</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>15.4214</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>18.3338</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>20.245</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>18.6192</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>17.4073</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>14.8278</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>11.647</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>19.2117</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>14.6453</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>14.2704</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>22.0369</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>15.5806</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>12.2829</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>10.0069</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>12.7175</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>13.8857</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>15.5612</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>22.6901</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>16.188</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>11.0255</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>18.7419</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>16.6015</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>13.0292</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>21.0245</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>18.6907</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>13.0211</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>19.8865</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>16.3844</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>18.3366</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>13.9499</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>17.2981</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>16.4827</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>14.4123</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>14.2434</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>13.0169</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>21.4513</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>16.1053</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>16.3439</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>11.0842</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>14.1546</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>16.6543</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>14.4534</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>13.8861</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>13.1506</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>18.9181</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>15.4739</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>12.9628</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>18.0571</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>10.0054</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>28.7283</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>14.4205</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>15.2737</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>116.577</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>11.3486</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>18.221</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>15.3657</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>13.7935</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>16.919</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>12.9361</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>17.4046</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>11.4357</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>14.9371</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>10.9978</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>17.0327</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>14.0548</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>11.0748</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="157353737"/>
+        <c:axId val="182648991"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="157353737"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="182648991"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="182648991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="157353737"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$499</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="499"/>
+                <c:pt idx="0">
+                  <c:v>797.741423</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>506.473452</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>652.797871</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>701.714821</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>793.174277</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>901.650954</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>896.200144</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>697.826507</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>505.557997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>539.252023</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>800.495227</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>404.718533</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>596.16942</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>53467.735973</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>598.449278</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>607.903494</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>797.633863</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>694.804227</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>651.612186</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>798.051188</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>546.637045</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>901.153353</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>708.468178</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>601.079685</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>705.532337</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>598.718129</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>693.189089</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>599.757352</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>543.775839</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>749.624437</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>800.237102</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>500.608907</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>757.653099</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>758.798719</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>693.041407</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>799.71951</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>652.836447</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>756.944014</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>802.792531</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>697.071065</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>602.93025</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>549.255599</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>751.376094</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>846.186355</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>501.567631</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>658.928672</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>691.944052</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>703.02885</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>744.061904</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>752.336819</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>747.950363</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>352.897068</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>443.174529</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>651.699275</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>705.34269</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>596.206869</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>503.842524</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>707.024703</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>603.654502</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>599.708575</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>851.653747</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>608.565804</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>752.946929</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>749.347863</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>498.711906</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>702.045018</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>547.521031</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>704.237713</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>701.795222</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>496.722018</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>743.937807</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>652.976532</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>856.397235</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>549.439414</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>749.194254</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>704.736239</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>746.059813</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>646.507905</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>748.634755</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>746.385168</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>551.295716</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>601.995325</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>558.046263</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>602.671523</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>505.769416</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>406.498642</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>546.294791</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>349.013622</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>403.089568</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>648.054335</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>598.671414</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>498.65557</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>404.316162</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>551.917664</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>653.170677</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>698.64447</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>641.200248</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>528.092011</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>604.461635</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>411.012659</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>591.189212</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>445.396863</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>467.840743</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>395.361353</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>797.006799</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>600.662361</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>603.469236</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>697.02937</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>532.843554</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>449.517472</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>701.959921</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>805.005022</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>598.786267</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>546.065153</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>496.595943</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>643.923318</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>573.074105</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>695.78885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>626.901296</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>700.053565</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>595.448969</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>545.623888</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>599.921086</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>651.745785</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>605.146674</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>550.524552</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>891.014753</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>651.864282</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>575.674219</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>994.094077</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>694.554626</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>703.794192</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>501.713801</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>676.091021</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>702.102848</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>602.736757</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>505.922015</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>502.354211</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>546.12275</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>529.309661</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>647.767221</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>670.326453</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>553.111785</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>600.658737</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>597.224547</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>600.501172</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>549.279549</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>501.891448</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>753.046312</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>593.33017</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>796.778991</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>801.872396</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>650.786571</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>596.952928</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>746.760185</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>794.633199</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>554.455742</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>674.376775</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>701.076806</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>699.980259</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>596.354497</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>670.278018</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>600.184564</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>697.974704</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>755.42529</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>731.919261</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>754.777172</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>697.083236</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>605.384774</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>696.235541</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>649.027427</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>694.23777</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>711.29615</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>500.689217</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>602.415414</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>634.972862</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>797.40833</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>595.37315</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>995.191611</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>696.17489</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>602.841689</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>999.638627</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>632.960467</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>599.112391</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>600.443332</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>811.977994</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>605.707586</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>648.901738</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>597.062713</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>597.023153</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>796.010473</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>599.49583</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>797.718035</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>598.587476</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>849.948198</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>604.374074</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>606.810162</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>799.759087</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>697.683122</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>545.123633</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>702.03251</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>895.33446</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>398.165275</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1053.09479</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>997.198933</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>800.868016</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>803.187447</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>547.132696</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>502.315147</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>851.924014</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>598.082828</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>600.54782</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>555.214322</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>567.650458</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>553.61556</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>632.719545</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>651.94279</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>630.670606</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>801.265272</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>602.710853</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>647.289917</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>702.024603</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>800.815365</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>602.872376</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>500.8151</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>730.322042</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>752.040126</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>696.693382</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>548.175508</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>601.886705</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>651.526003</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>398.199971</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>601.060092</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>599.528885</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>649.220954</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>594.043765</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>552.514957</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>700.081519</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>699.88982</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>598.731969</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>546.618989</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>504.124003</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>597.311433</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>502.466879</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>599.283561</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>492.530094</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>601.791873</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>498.278191</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>400.798498</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>595.499543</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>494.875193</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>695.116647</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>651.34529</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>506.016446</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>450.840474</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>794.657477</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>352.501533</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>797.250937</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>592.109892</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>500.970497</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>649.338811</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>500.79661</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>447.334498</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>595.457899</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>704.503276</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>503.519083</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>542.666276</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>730.121601</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>597.15907</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>599.783246</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>699.229032</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>700.234831</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>657.148068</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>595.618991</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>600.453457</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>700.686439</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>755.710353</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>595.250541</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>698.26326</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>508.831743</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>643.891522</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>606.570955</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>550.19652</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>596.016963</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>604.018557</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>508.789066</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>595.802905</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>694.938807</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>596.286907</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>704.514434</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>599.089058</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>699.582412</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>644.514859</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>600.559195</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>602.39467</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>693.925923</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>397.372987</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>605.839124</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>598.671517</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>894.250712</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>603.238492</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>692.633829</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>646.85901</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>604.517721</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>647.818928</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>694.878077</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>547.205365</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>600.50186</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>696.567731</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>700.517431</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>599.431787</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>601.969498</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>697.754722</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>594.021313</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>550.200741</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>599.24574</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>400.487514</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>597.650985</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>701.900227</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>601.059695</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>596.093119</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>700.826596</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>601.991032</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>553.877195</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>602.477533</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>744.895314</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>699.402689</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>598.285296</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>512.381036</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>550.523788</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>508.919384</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>599.173536</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>597.912147</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>545.312969</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>595.75007</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>653.906107</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>699.611336</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>606.164537</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>600.997404</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>747.924594</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>592.477185</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>602.818846</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>653.561939</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>707.675505</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>548.894133</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>601.229415</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>489.450651</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>693.963025</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>550.020175</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>497.720675</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>801.827914</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>695.43814</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>595.997715</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>548.873406</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>607.103177</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>698.971013</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>690.711717</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>901.948652</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>591.924276</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>702.068595</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>597.859845</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>552.647497</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>666.043626</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>656.48163</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>605.735245</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>604.632722</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>598.496975</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>651.246688</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>627.908439</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>744.556585</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>604.230425</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>694.817162</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>702.70875</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>704.566879</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>749.171551</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>595.360128</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>593.644081</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>698.02723</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>901.932109</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>601.468775</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>697.328862</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>670.011858</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>747.112237</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>698.12104</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>650.340175</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>627.461225</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>698.301937</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>674.531801</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>650.056925</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>525.874779</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>846.124847</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>895.502691</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>600.989925</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>505.030884</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>847.555957</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>627.588717</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>694.840939</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>547.69822</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>602.491415</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>728.742657</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>748.650971</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>571.390237</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>650.062615</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>801.721202</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>494.421995</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>503.340412</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>548.481547</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>630.442688</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>649.579464</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>803.266105</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>593.562878</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>694.121821</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>806.404919</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>505.250466</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>605.930007</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>605.054777</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>747.707623</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>631.073092</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>594.945605</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>536.538904</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>498.824353</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>702.485885</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>648.65913</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>701.448127</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>847.987068</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>728.776414</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>699.498431</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>605.116629</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>957.221802</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>702.751584</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>556.768524</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>703.1461</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>555.227927</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>596.21074</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>748.450666</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>594.077458</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>598.693465</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>599.616536</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>547.082099</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>729.780763</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>651.4222</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>693.958048</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>594.140897</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>483.408589</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>951.531663</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>801.804923</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>702.211434</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>570.659877</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>997.648378</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>497.162265</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>699.33823</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>524.161899</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>646.484799</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>667.41713</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>750.519452</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>701.474459</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>700.673152</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>727.435756</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>642.520036</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>498.126745</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>798.84652</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>804.781603</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>802.726981</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>981.626312</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>643.898974</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>417.669502</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>504.906821</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>697.214037</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1097.495174</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>776.978209</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>697.199504</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>582.060018</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>998.640031</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1190.298893</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>598.754945</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>525.605671</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>956.761549</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>892.288314</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>500.622335</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>799.385555</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>744.762695</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>726.916699</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>949.285373</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>598.713289</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>659.435208</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>810.678889</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>539.084101</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>693.824656</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>751.354134</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>820.894318</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>895.328133</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>899.00828</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>801.819589</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>803.104428</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>746.914081</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>869.761476</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>1002.007169</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1198.778739</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>996.271661</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="284908097"/>
+        <c:axId val="510067953"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="284908097"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="510067953"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="510067953"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="284908097"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="0" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$499</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="499"/>
+                <c:pt idx="0">
+                  <c:v>775.315592</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1550.490182</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2080.025189</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2719.10886</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3399.912951</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4179.572357</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5065.29487</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5947.269619</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6631.699858</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7123.002871</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7694.649738</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8480.537438</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8871.20901</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8556.571094</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8074.693003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8260.917689</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8163.221696</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8274.272579</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8275.144936</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7944.517638</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7847.640248</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7769.187575</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8145.584917</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8408.097256</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8166.882288</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8448.383301</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8364.638102</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8520.33812</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8461.29215</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8216.977299</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8272.968502</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8374.332065</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8127.934458</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8380.949761</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8167.312873</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8182.18307</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8374.328009</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8312.041245</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8481.528822</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8629.476592</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8717.030873</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8755.02861</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8564.854963</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8515.476252</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8877.040274</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8593.283401</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8479.321145</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8465.37568</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8366.944681</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8423.451024</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8374.08358</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8317.827102</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7972.364702</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7772.536822</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7919.633308</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7876.420291</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7671.529275</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7765.706941</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7817.087807</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7788.854038</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7661.530814</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7871.486675</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7727.039551</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>7725.053197</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>8106.422537</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>8175.838729</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>8210.826868</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>8069.422525</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>8225.172991</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>8369.794881</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>8069.411616</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>8165.961877</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>8275.624427</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8236.353865</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>8117.266288</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>8102.794464</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>8061.227445</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>8322.188161</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>8266.340923</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>8477.446576</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>8473.378686</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>8304.995664</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8417.624553</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>8280.863327</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>8269.781607</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7913.988703</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>7778.23268</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7545.357358</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>7190.932965</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6859.487615</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6872.111426</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6714.025212</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6447.62465</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6371.235122</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6270.0183</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5729.061593</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5725.847975</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5306.555992</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5352.160959</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4842.691973</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4916.937784</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4631.865154</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4394.811775</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>3814.026226</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>3721.318958</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>3396.028982</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>3393.177318</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>3473.743685</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>3403.528452</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>3500.72846</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>3366.30328</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>3386.037963</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>3623.712868</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>3614.727229</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3654.693571</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>3724.672396</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3749.487434</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>3931.698645</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3685.620346</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>3867.637581</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>3679.12261</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>3918.950801</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>3669.533608</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4012.952176</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>3503.72996</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>3868.275423</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>3513.939279</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>3882.384545</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>3865.714932</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>3912.783938</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>3886.766434</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4176.777452</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>3963.753581</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4036.417408</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4032.581813</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4197.426333</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4185.112269</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4092.394592</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4088.749924</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4054.632209</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>3791.792663</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>3950.28851</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>3860.66253</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>3684.716598</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3706.697599</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3654.462563</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>3667.705125</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3604.443149</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>3483.141406</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>3483.100469</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3679.080187</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3577.358922</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3916.687075</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3772.372753</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3931.522329</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3764.673192</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4123.732636</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3870.166618</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4083.333745</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3976.49273</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4232.484834</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4201.47358</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4072.976005</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4337.040297</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3916.627561</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4136.528659</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4076.996045</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4273.248881</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4110.685641</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4165.763863</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4160.53747</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4196.574123</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4123.271837</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4203.290205</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4279.413515</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4072.665904</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4275.493196</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4083.857046</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4272.666387</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3858.634966</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4250.999889</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4100.725366</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4277.652696</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4395.467567</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4346.733483</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4337.720774</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4286.625004</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4690.344494</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4260.664984</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4557.563009</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4131.95589</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4566.13902</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4154.128855</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4283.405246</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4352.640624</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>3912.949076</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4459.377377</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3970.88027</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4373.84263</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3907.221553</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4457.151426</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3850.45317</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4494.284313</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>4144.294594</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4086.426484</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4638.561573</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>4287.647107</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4855.357134</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4305.86158</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4699.827442</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4185.204339</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4650.377033</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4281.999128</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4708.913542</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4087.588808</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4364.265867</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4305.874197</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>4025.863935</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4009.73852</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3800.436394</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4010.795269</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3937.548167</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4147.777431</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>3965.345361</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4227.546938</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>3977.641473</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4177.802409</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4163.708943</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4310.349524</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4145.342147</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4179.539238</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4073.85662</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4016.760262</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>3870.843702</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>3980.787221</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>3667.514967</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>3876.623788</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>3661.57915</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>3874.589512</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3578.030959</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3780.111388</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>3604.461354</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3769.106801</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3472.566813</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>3727.836758</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3559.158863</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>3583.443287</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3544.916399</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3574.696391</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>3469.127124</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3386.15509</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>3366.742695</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>3162.071975</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>3464.859891</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3265.237136</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3365.275701</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3150.463671</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3450.502474</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3171.221794</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>3686.985798</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3211.445934</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3662.910052</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3411.816059</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>3664.782522</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3431.759679</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3437.532722</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3419.296183</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>3522.733648</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3533.967516</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>3645.338622</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>3518.942076</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3460.200369</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>3589.646908</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>3656.90854</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>3628.046387</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>3768.397068</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>3870.252974</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>3871.12077</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>3879.321059</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3977.165394</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4035.598253</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3779.913505</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4057.199997</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>3766.537541</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>3933.313249</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>3660.617609</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>3879.338258</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>3589.214195</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>3877.493238</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>3645.363511</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>3667.614485</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>3863.821522</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>3572.06171</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>3968.378379</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>3662.735095</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>3874.604383</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>3671.964704</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>3797.857814</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>3645.115438</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>3905.056565</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>3650.484248</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>3961.605478</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>3776.745028</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>3854.50331</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>3820.986381</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3766.480894</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>3759.973121</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>3884.054636</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>3757.299775</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>3979.101881</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>3857.666447</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4038.880818</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>3905.475716</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>3858.640726</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>3863.725536</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>3755.787186</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>3807.007109</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>3702.51439</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>3649.436417</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>3636.708596</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>3763.33263</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>3612.577122</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>3668.732136</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>3655.175357</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>3664.024302</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>3607.729109</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>3653.026795</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>3736.513032</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>3782.448616</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>3818.538325</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>3861.136526</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>3782.24456</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>3672.426453</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>3769.382962</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>3672.84905</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3578.296374</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>3665.007342</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>3725.89845</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>3785.091404</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>3614.422652</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>3576.11724</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>3684.69356</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>3736.5806</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>3746.889607</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>3793.395002</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3882.838693</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>3769.861784</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>3794.320996</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>3796.414023</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>3814.593461</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>3654.733355</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>3664.914995</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>3855.390716</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>3688.25035</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>3845.534792</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>3623.056036</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>3754.948156</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3660.081841</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>3838.314891</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3962.191998</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3920.736321</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4032.761647</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3989.76295</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4064.074532</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3853.590199</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4077.203532</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3868.042</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4117.512616</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3933.63104</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4029.454834</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>3862.693322</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>3869.590886</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3867.794175</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3905.010531</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3921.377206</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4057.175642</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4033.268019</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3945.67383</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3986.034909</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4088.203417</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4286.494128</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4054.404206</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4306.21434</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4031.568929</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4361.379732</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4038.293586</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4314.656849</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>3953.872969</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4266.992946</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4019.651189</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4366.422246</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>3881.682817</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4284.225373</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4057.93023</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4183.105253</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4028.162357</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4184.765785</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4036.365167</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4228.035369</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4043.036286</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4115.635822</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4092.043598</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4197.678972</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4168.984439</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4026.785433</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4060.754193</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3967.921378</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4148.83451</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>3786.692144</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>3981.927407</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>3834.994463</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4173.109497</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>3763.32311</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4081.679607</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>3867.203358</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4077.932118</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>3821.686745</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>3920.967347</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4065.169474</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4143.71392</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4076.432734</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4068.177474</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>3850.119631</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>3933.773946</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>3957.730009</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4036.261682</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4018.40572</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4273.626213</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4124.001686</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4267.234399</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4363.661431</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4284.97219</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4384.219188</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4380.97821</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4421.554491</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4176.559435</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4562.20547</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4097.036431</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4269.125621</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>3954.056382</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4061.691868</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4073.63303</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3726.122284</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>3946.290936</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>3709.77689</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>3759.928664</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4124.692042</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>3983.09257</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4080.394996</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>3937.440017</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>3968.269856</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4339.346404</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4127.058716</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4061.848142</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4116.216699</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4067.495954</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4260.979832</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4268.008246</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4017.371078</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4170.565765</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3917.4567</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4135.444923</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>4231.025451</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4003.198961</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4326.241009</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4446.221099</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4314.307151</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4282.101923</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4062.655479</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4206.970444</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>4470.914591</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4278.37441</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4522.823254</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4350.507007</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4735.77444</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4674.05855</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>4560.397278</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>4263.676226</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>4916.112394</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4746.521001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>4920.312879</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>4851.318841</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>4555.386118</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>4799.772123</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4802.250266</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4725.558868</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4484.447141</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>4471.414205</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>4387.655119</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>4639.678391</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>4166.923214</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>4544.580294</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>4568.040883</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>4684.403306</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>4618.672512</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>4686.749036</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>4463.425094</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>4945.252067</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>4753.462069</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="396506893"/>
+        <c:axId val="470009991"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="396506893"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470009991"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="470009991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="396506893"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$499</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="499"/>
+                <c:pt idx="0">
+                  <c:v>1598.050615</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2077.566134</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2745.91086</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3435.462581</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4213.235628</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5094.905211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5975.632414</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6657.398426</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7149.576055</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7675.425794</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8511.184665</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8896.332971</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9480.39963</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>62043.931067</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8684.910081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8888.589383</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8987.104959</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8981.199606</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8954.493022</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8794.182526</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8413.452893</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8688.482128</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8883.110395</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9032.321641</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8891.247825</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9073.95883</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9105.811291</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9167.608272</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9025.020389</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8987.156436</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9088.595604</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8898.559472</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8901.808457</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9149.56658</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8889.04148</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8993.57208</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>9041.114656</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>9081.465459</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>9298.006953</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9338.715457</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9337.186823</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9317.157209</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>9327.664257</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>9378.203907</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9395.115005</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9274.350673</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9186.671197</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9181.70573</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9131.514285</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9187.648643</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9133.488743</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8688.65767</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>8429.055931</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>8436.211797</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>8634.731298</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>8485.26026</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>8187.287399</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>8484.710244</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>8436.450109</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8418.109413</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8524.702961</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>8495.840979</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>8490.34698</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8485.64186</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>8621.771743</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>8895.276147</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>8779.547099</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>8788.784638</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>8937.844213</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>8887.222299</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>8827.796623</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>8833.040909</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9145.952062</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8800.681079</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>8880.158642</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>8823.300603</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>8817.225758</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>8981.545466</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>9032.587878</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>9236.983144</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>9037.037102</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>8921.748689</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8989.782516</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>8895.27995</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>8786.028523</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>8331.813145</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>8338.209871</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7921.80718</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>7620.607733</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>7522.74445</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>7486.18884</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7228.198882</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6869.847512</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6941.479986</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6937.144777</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6452.781863</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6379.904923</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5851.304303</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5976.606994</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5265.161232</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5518.608596</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5094.317917</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4881.357718</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4223.924179</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4531.564857</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4007.735843</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4010.168254</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4183.748955</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>3957.334306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>3961.616832</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4088.396201</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4216.444885</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4236.666635</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4179.673782</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4164.696514</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4394.240114</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4333.612839</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4639.341195</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4326.490242</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4578.680246</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4286.437479</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4486.981789</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4284.374194</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4681.068561</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4124.525734</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4430.369675</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4415.968132</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4546.018627</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4459.097451</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4920.866815</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4593.62206</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4900.953444</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4481.564682</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4725.585829</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4749.379261</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4811.69249</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4708.335484</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4615.549203</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4654.005474</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4605.62897</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4455.785384</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4632.684063</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4433.833815</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4302.906935</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4316.816646</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4267.249335</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4228.551674</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4118.485597</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4249.697418</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4088.492039</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4486.318478</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4390.192118</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4584.299946</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4386.631881</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4691.338814</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4578.328391</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4689.701678</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4563.940093</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4795.446351</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4688.921189</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4838.732131</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4886.185598</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4684.253569</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5054.693901</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4686.126351</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4886.78742</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4844.396917</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4993.080317</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4727.011715</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4876.948204</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4823.057397</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4910.327193</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4844.752887</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4715.445122</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4894.754729</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4718.061766</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5084.554326</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4690.440696</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5278.995498</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4568.973656</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4865.496678</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5111.225893</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4921.621363</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5010.019558</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4963.064015</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5168.831568</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4915.07949</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5351.975532</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4871.725797</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5165.950862</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4940.075063</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5181.61475</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4968.61769</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4893.204622</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5213.899322</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4529.28695</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5080.168239</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4785.109557</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>5086.204752</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4463.581486</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5174.017436</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4760.50173</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4910.492288</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5210.511784</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>5105.107917</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>5458.099489</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>5109.477954</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5413.90023</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4822.365327</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5575.739856</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4793.626867</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5264.511253</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4849.78905</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>5289.4662</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4656.273068</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5011.806512</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4970.442387</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>4668.872741</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4829.175292</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>4420.050547</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4669.525186</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>4659.70977</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4965.762396</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4586.543137</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4739.443638</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4720.561515</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4940.792135</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4875.801625</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4879.547932</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4767.387852</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4842.836641</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4490.307091</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4628.958654</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4485.148387</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4648.740075</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4282.005532</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4441.400345</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4383.435569</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4586.698432</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4192.752128</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4337.085977</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4120.269657</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4382.768634</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3998.084792</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4336.903819</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4066.955757</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4205.45966</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>4061.36719</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3987.461789</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4079.286267</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3894.206483</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4077.882842</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>3828.403265</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>3991.022337</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3733.92951</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4174.743978</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3525.095604</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>4263.601911</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3779.289186</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>4207.204995</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3881.876145</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>4182.628262</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3873.587857</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4277.814821</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>4148.375855</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3954.182505</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3981.160459</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4264.077249</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4143.204486</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4257.434868</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4229.359308</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4172.5598</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4267.022376</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4267.628931</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4245.025744</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4486.314407</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4639.741027</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>4478.475011</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4594.224319</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>4501.386137</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4693.084875</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4398.52726</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4618.724917</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>4382.631204</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4550.813706</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4197.304175</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4486.881363</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4303.329502</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4485.308145</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4368.702745</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4278.515643</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4575.069134</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4227.747669</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4585.560074</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4280.531765</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4581.051206</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4081.673691</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4417.267338</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4261.594955</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4811.135277</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4264.59984</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4677.649807</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4434.231838</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>4476.238031</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4480.240909</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4479.044271</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4379.197386</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4507.826396</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>4464.545606</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4691.088912</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4470.132734</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4654.773616</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4614.256838</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4464.496739</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4425.237977</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>4378.191726</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4225.849323</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4312.055775</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>4362.285344</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4249.038991</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4377.777549</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4325.533918</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4288.298768</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4224.437952</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>4280.473535</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>4368.906423</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>4365.308984</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>4348.589228</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4318.693652</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4385.919713</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4386.66001</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4393.965096</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4290.1029</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4327.528931</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4289.74412</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4243.888181</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4376.620078</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4344.585887</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4397.770708</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4385.917646</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4185.234625</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4307.721106</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4405.369939</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4466.284512</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4356.361235</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4499.328308</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4274.073135</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4505.004021</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4363.896498</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4330.238436</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4466.865769</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4381.550535</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4462.530931</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4257.018456</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4467.044069</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4344.141149</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4457.175873</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>4585.613393</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4445.515467</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4684.234793</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4530.451666</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4604.991144</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4675.012976</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4733.837662</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4471.960744</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4693.492554</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4485.659575</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4781.552804</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4581.303179</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4787.036419</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4493.744947</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4580.725248</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4586.490125</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4621.48741</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4682.213957</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4664.11457</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4638.1779</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4660.80926</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4901.136818</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4711.528092</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>5005.77869</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4735.081064</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>5071.631277</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4747.746969</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>5034.082807</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4680.636611</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>5033.137086</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4639.14997</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4937.279571</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4559.325968</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>5234.084093</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4788.203108</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4896.473198</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4580.017814</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>5042.40721</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4671.519974</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4893.762924</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4597.079187</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4842.692584</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4788.372743</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4879.586693</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4682.643435</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4863.402287</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4983.851241</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4532.994928</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4582.160405</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4538.038725</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4790.311798</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4454.405708</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4802.747112</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4440.448941</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4886.528718</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4589.573729</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4597.212073</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4488.540065</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4696.602095</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4588.452968</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4568.509639</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4673.675779</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4693.300124</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4586.526487</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4787.994959</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4511.424461</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4647.210673</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4816.534977</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4783.159896</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4738.138351</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4895.013242</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>5092.995988</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4986.312883</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4943.543855</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4998.33199</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4951.590815</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4992.61035</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>5188.338957</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4790.881893</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5179.518135</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4714.060267</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4831.03552</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4695.484145</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4732.325768</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4782.236378</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4334.533581</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4451.736425</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4676.889153</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4574.016487</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4836.910376</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4566.469947</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5091.929074</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4450.163482</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4690.298186</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4879.696303</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4784.569015</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4748.007172</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4883.337651</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4781.999613</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4982.677484</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>5014.134702</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4672.912214</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4688.57901</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4732.68762</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4958.563126</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5047.702332</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5002.123373</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4986.622683</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4878.302901</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4833.457372</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4992.33286</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5181.601953</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>5000.053953</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>5184.457995</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4871.518628</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5535.617885</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5557.4602</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>5348.982785</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>5213.550321</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5530.309427</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>5174.88264</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5432.208629</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5558.869356</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5683.132674</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5588.24094</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5533.399791</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5412.905912</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>5476.959174</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5652.814757</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5034.879842</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5183.459861</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5154.374953</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5474.366209</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5079.170347</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5456.524674</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5387.265072</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5498.943434</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5380.523693</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5567.508312</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5482.464963</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>6158.085606</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>5760.80853</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="702440657"/>
+        <c:axId val="54184953"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="702440657"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="54184953"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="54184953"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="702440657"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="0" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>145415</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3492500" y="3657600"/>
+        <a:ext cx="7511415" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3479800" y="6692900"/>
+        <a:ext cx="7518400" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>889000</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>145415</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3308350" y="584200"/>
+        <a:ext cx="7695565" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>151765</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3613150" y="9702800"/>
+        <a:ext cx="7397115" cy="4635500"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8484,5 +17875,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>